--- a/Screen_Printing_RND_Technical_Library_Workbook.xlsx
+++ b/Screen_Printing_RND_Technical_Library_Workbook.xlsx
@@ -2340,7 +2340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2475,266 +2475,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RND-REC-2026-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ST-2026-GYMSHARK-01</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Silicone Rubber</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Durability Lab Exec</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>v2.1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>95% Cotton / 5% Elastane</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Charcoal Dark Grey</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Single Jersey (Knitted)</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>220 GSM</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Yes (Anti-Bleed Barrier)</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>[{"Delete": false, "Role": "Base Transparent", "Product Name": "Silicone Base Clear", "Code": "SIL-BASE-90", "Percentage (%)": 70.0, "Use Quantity (g)": 700.0, "Mixing Notes": "High elasticity base"}, {"Delete": false, "Role": "Base Opaque / White", "Product Name": "Silicone White Undercoat", "Code": "SIL-WHT-10", "Percentage (%)": 20.0, "Use Quantity (g)": 200.0, "Mixing Notes": "Provides opacity &amp; bleed barrier"}, {"Delete": false, "Role": "Pigment Colorant", "Product Name": "High Fastness Black Pigment", "Code": "PIG-BLK-05", "Percentage (%)": 5.0, "Use Quantity (g)": 50.0, "Mixing Notes": "Color shade matching"}, {"Delete": false, "Role": "Catalyst / Hardener", "Product Name": "Silicone Platinum Catalyst", "Code": "CAT-SIL-02", "Percentage (%)": 2.0, "Use Quantity (g)": 20.0, "Mixing Notes": "Mix thoroughly before printing"}, {"Delete": false, "Role": "Crosslinker / Fixer", "Product Name": "Anti-Fading Crosslinker", "Code": "XL-MOD-01", "Percentage (%)": 3.0, "Use Quantity (g)": 30.0, "Mixing Notes": "Enhances wash fastness (20+ cycles)"}]</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>120T (305 Mesh)</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>70/90/70 Triple</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>75° / Medium Speed</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2.5 mm</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>110°C / 5 Seconds</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>100°C</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>90sec</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2 Print - 1 Flash - 2 Print</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RND-REC-2026-002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ST-2026-GYMSHARK-01</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Silicone Rubber</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Durability Lab Exec</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>v2.1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>95% Cotton / 5% Elastane</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Charcoal Dark Grey</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Single Jersey (Knitted)</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>220 GSM</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Yes (Anti-Bleed Barrier)</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>[{"Delete": false, "Role": "Base Transparent", "Product Name": "Silicone Base Clear", "Code": "SIL-BASE-90", "Percentage (%)": 70.0, "Use Quantity (g)": 700.0, "Mixing Notes": "High elasticity base"}, {"Delete": false, "Role": "Base Opaque / White", "Product Name": "Silicone White Undercoat", "Code": "SIL-WHT-10", "Percentage (%)": 20.0, "Use Quantity (g)": 200.0, "Mixing Notes": "Provides opacity &amp; bleed barrier"}, {"Delete": false, "Role": "Pigment Colorant", "Product Name": "High Fastness Black Pigment", "Code": "PIG-BLK-05", "Percentage (%)": 5.0, "Use Quantity (g)": 50.0, "Mixing Notes": "Color shade matching"}, {"Delete": false, "Role": "Catalyst / Hardener", "Product Name": "Silicone Platinum Catalyst", "Code": "CAT-SIL-02", "Percentage (%)": 2.0, "Use Quantity (g)": 20.0, "Mixing Notes": "Mix thoroughly before printing"}, {"Delete": false, "Role": "Crosslinker / Fixer", "Product Name": "Anti-Fading Crosslinker", "Code": "XL-MOD-01", "Percentage (%)": 3.0, "Use Quantity (g)": 30.0, "Mixing Notes": "Enhances wash fastness (20+ cycles)"}]</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>120T (305 Mesh)</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>70/90/70 Triple</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>75° / Medium Speed</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2.5 mm</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>110°C / 5 Seconds</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>100°C</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>90sec</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2 Print - 1 Flash - 2 Print</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
